--- a/docs/lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD252FB-8628-884B-A216-C72D93FD5A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB00940-C1E7-D046-9B4E-EA94E4AF8538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -712,16 +712,16 @@
     <t>M...1234(256)</t>
   </si>
   <si>
-    <t>Save product does not throw exceptions</t>
-  </si>
-  <si>
-    <t>Now service has validator and throws exception</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validator doesn’t throw for max len of string being passed or null </t>
+  </si>
+  <si>
+    <t>Now validator has what it needs</t>
   </si>
 </sst>
 </file>
@@ -4232,35 +4232,35 @@
         <v>51</v>
       </c>
       <c r="C28" s="18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D28" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E28" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="97" t="s">
         <v>139</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H28" s="97" t="s">
-        <v>141</v>
       </c>
       <c r="I28" s="98"/>
       <c r="J28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="21">
         <v>0</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N28" s="2">
         <v>10</v>

--- a/docs/lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB00940-C1E7-D046-9B4E-EA94E4AF8538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C673B99B-17E8-A44A-BCC3-BED802C36410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="35840" windowHeight="22400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="143">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -1372,7 +1372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1475,242 +1475,232 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2064,12 +2054,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
       <c r="H1" s="31" t="s">
         <v>1</v>
       </c>
@@ -2077,11 +2067,11 @@
       <c r="J1" s="31"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H3" s="2"/>
@@ -2232,21 +2222,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="28"/>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C26" s="30"/>
@@ -2288,41 +2278,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="77"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="G5" s="49" t="s">
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="G5" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="51"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="66"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="10" t="s">
@@ -2337,37 +2327,37 @@
       <c r="E6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="65" t="s">
+      <c r="G6" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="71" t="s">
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="71"/>
+      <c r="O6" s="56"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="70" t="s">
         <v>69</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="70"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10" t="s">
         <v>90</v>
       </c>
@@ -2383,16 +2373,16 @@
       <c r="M7" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="N7" s="54" t="s">
+      <c r="N7" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="72"/>
+      <c r="O7" s="58"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="56"/>
+      <c r="C8" s="70"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>72</v>
@@ -2418,16 +2408,16 @@
       <c r="M8" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="N8" s="67" t="s">
+      <c r="N8" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="O8" s="68"/>
+      <c r="O8" s="63"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="70" t="s">
         <v>70</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2455,16 +2445,16 @@
       <c r="M9" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="67" t="s">
+      <c r="N9" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="O9" s="68"/>
+      <c r="O9" s="63"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="56"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>73</v>
@@ -2490,16 +2480,16 @@
       <c r="M10" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N10" s="67" t="s">
+      <c r="N10" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="O10" s="68"/>
+      <c r="O10" s="63"/>
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="71" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="35" t="s">
@@ -2527,16 +2517,16 @@
       <c r="M11" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N11" s="67" t="s">
+      <c r="N11" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="O11" s="68"/>
+      <c r="O11" s="63"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>75</v>
@@ -2562,16 +2552,16 @@
       <c r="M12" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N12" s="67" t="s">
+      <c r="N12" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="O12" s="68"/>
+      <c r="O12" s="63"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2599,16 +2589,16 @@
       <c r="M13" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="67" t="s">
+      <c r="N13" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="O13" s="68"/>
+      <c r="O13" s="63"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="60"/>
+      <c r="C14" s="74"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>77</v>
@@ -2634,16 +2624,16 @@
       <c r="M14" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N14" s="67" t="s">
+      <c r="N14" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="O14" s="68"/>
+      <c r="O14" s="63"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="70" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -2657,14 +2647,14 @@
       <c r="K15" s="39"/>
       <c r="L15" s="39"/>
       <c r="M15" s="39"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="63"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="56"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
         <v>80</v>
@@ -2683,7 +2673,7 @@
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="56"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
         <v>83</v>
@@ -2695,14 +2685,14 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="75"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="61"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="70" t="s">
         <v>81</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2716,14 +2706,14 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="75"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="61"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="56"/>
+      <c r="C19" s="70"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
         <v>82</v>
@@ -2735,14 +2725,14 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="75"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="61"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="70" t="s">
         <v>84</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2756,14 +2746,14 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="75"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="61"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="4">
         <v>15</v>
       </c>
-      <c r="C21" s="56"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
         <v>86</v>
@@ -2773,7 +2763,7 @@
       <c r="B22" s="36">
         <v>16</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="67" t="s">
         <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2785,32 +2775,18 @@
       <c r="B23" s="37">
         <v>17</v>
       </c>
-      <c r="C23" s="53"/>
+      <c r="C23" s="68"/>
       <c r="D23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
     <mergeCell ref="G5:O5"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="I6:M6"/>
@@ -2827,6 +2803,20 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2850,7 +2840,7 @@
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="120" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="46" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.33203125" customWidth="1"/>
@@ -2858,42 +2848,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="77"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
     </row>
     <row r="6" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
@@ -2906,47 +2896,47 @@
         <v>36</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="65" t="s">
+      <c r="G6" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="65" t="s">
+      <c r="I6" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="82" t="s">
+      <c r="K6" s="83" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="84"/>
       <c r="M6" s="84"/>
       <c r="N6" s="84"/>
-      <c r="O6" s="82" t="s">
+      <c r="O6" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="P6" s="83"/>
+      <c r="P6" s="87"/>
     </row>
     <row r="7" spans="2:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="59">
+      <c r="B7" s="73">
         <v>1</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="71" t="s">
         <v>107</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="70"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="55"/>
       <c r="K7" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L7" s="121" t="s">
+      <c r="L7" s="47" t="s">
         <v>92</v>
       </c>
       <c r="M7" s="16" t="s">
@@ -2955,191 +2945,191 @@
       <c r="N7" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="O7" s="54" t="s">
+      <c r="O7" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="72"/>
+      <c r="P7" s="58"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="76"/>
-      <c r="C8" s="77"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="2" t="s">
         <v>109</v>
       </c>
       <c r="G8" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="114">
+      <c r="H8" s="4">
         <v>1</v>
       </c>
-      <c r="I8" s="115" t="s">
+      <c r="I8" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="115" t="s">
+      <c r="J8" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K8" s="116" t="s">
+      <c r="K8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L8" s="122">
+      <c r="L8" s="48">
         <v>15.5</v>
       </c>
-      <c r="M8" s="116" t="s">
+      <c r="M8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N8" s="116" t="s">
+      <c r="N8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O8" s="117" t="s">
+      <c r="O8" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="P8" s="118"/>
+      <c r="P8" s="82"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="76"/>
-      <c r="C9" s="77"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G9" s="10">
         <v>2</v>
       </c>
-      <c r="H9" s="114">
+      <c r="H9" s="4">
         <v>2</v>
       </c>
-      <c r="I9" s="115" t="s">
+      <c r="I9" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="115" t="s">
+      <c r="J9" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K9" s="119" t="s">
+      <c r="K9" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="122">
+      <c r="L9" s="48">
         <v>15.5</v>
       </c>
-      <c r="M9" s="116" t="s">
+      <c r="M9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N9" s="116" t="s">
+      <c r="N9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O9" s="117" t="s">
+      <c r="O9" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="P9" s="118"/>
+      <c r="P9" s="82"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="76"/>
-      <c r="C10" s="77"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="G10" s="10">
         <v>3</v>
       </c>
-      <c r="H10" s="114">
+      <c r="H10" s="4">
         <v>3</v>
       </c>
-      <c r="I10" s="115" t="s">
+      <c r="I10" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="115" t="s">
+      <c r="J10" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K10" s="119" t="s">
+      <c r="K10" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="L10" s="122">
+      <c r="L10" s="48">
         <v>15.5</v>
       </c>
-      <c r="M10" s="116" t="s">
+      <c r="M10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N10" s="116" t="s">
+      <c r="N10" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="117" t="s">
+      <c r="O10" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="P10" s="118"/>
+      <c r="P10" s="82"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="76"/>
-      <c r="C11" s="77"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="2" t="s">
         <v>112</v>
       </c>
       <c r="G11" s="10">
         <v>4</v>
       </c>
-      <c r="H11" s="114">
+      <c r="H11" s="4">
         <v>4</v>
       </c>
-      <c r="I11" s="115" t="s">
+      <c r="I11" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="115" t="s">
+      <c r="J11" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K11" s="119" t="s">
+      <c r="K11" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="48">
         <v>15.5</v>
       </c>
-      <c r="M11" s="116" t="s">
+      <c r="M11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N11" s="116" t="s">
+      <c r="N11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="117" t="s">
+      <c r="O11" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="P11" s="118"/>
+      <c r="P11" s="82"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B12" s="60"/>
-      <c r="C12" s="58"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="2" t="s">
         <v>113</v>
       </c>
       <c r="G12" s="10">
         <v>5</v>
       </c>
-      <c r="H12" s="114">
+      <c r="H12" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="115" t="s">
+      <c r="I12" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="115" t="s">
+      <c r="J12" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K12" s="119" t="s">
+      <c r="K12" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="L12" s="122">
+      <c r="L12" s="48">
         <v>15.5</v>
       </c>
-      <c r="M12" s="116" t="s">
+      <c r="M12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N12" s="116" t="s">
+      <c r="N12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O12" s="117" t="s">
+      <c r="O12" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="P12" s="118"/>
+      <c r="P12" s="82"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B13" s="59">
+      <c r="B13" s="73">
         <v>2</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>114</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3148,337 +3138,345 @@
       <c r="G13" s="10">
         <v>6</v>
       </c>
-      <c r="H13" s="114">
+      <c r="H13" s="4">
         <v>6</v>
       </c>
-      <c r="I13" s="115" t="s">
+      <c r="I13" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K13" s="119" t="s">
+      <c r="K13" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="L13" s="122">
+      <c r="L13" s="48">
         <v>15.5</v>
       </c>
-      <c r="M13" s="116" t="s">
+      <c r="M13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N13" s="116" t="s">
+      <c r="N13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O13" s="117" t="s">
+      <c r="O13" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="P13" s="118"/>
+      <c r="P13" s="82"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="2" t="s">
         <v>116</v>
       </c>
       <c r="G14" s="10">
         <v>7</v>
       </c>
-      <c r="H14" s="114">
+      <c r="H14" s="4">
         <v>7</v>
       </c>
-      <c r="I14" s="115" t="s">
+      <c r="I14" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="J14" s="115" t="s">
+      <c r="J14" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="116" t="s">
+      <c r="K14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L14" s="122">
+      <c r="L14" s="48">
         <v>0</v>
       </c>
-      <c r="M14" s="116" t="s">
+      <c r="M14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N14" s="116" t="s">
+      <c r="N14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O14" s="117" t="s">
+      <c r="O14" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="118"/>
+      <c r="P14" s="82"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88"/>
       <c r="D15" s="2" t="s">
         <v>117</v>
       </c>
       <c r="G15" s="10">
         <v>8</v>
       </c>
-      <c r="H15" s="114">
+      <c r="H15" s="4">
         <v>8</v>
       </c>
-      <c r="I15" s="115" t="s">
+      <c r="I15" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="J15" s="115" t="s">
+      <c r="J15" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K15" s="116" t="s">
+      <c r="K15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L15" s="122">
+      <c r="L15" s="48">
         <v>0.01</v>
       </c>
-      <c r="M15" s="116" t="s">
+      <c r="M15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N15" s="116" t="s">
+      <c r="N15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O15" s="117" t="s">
+      <c r="O15" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="P15" s="118"/>
+      <c r="P15" s="82"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="2"/>
       <c r="G16" s="10">
         <v>9</v>
       </c>
-      <c r="H16" s="114">
+      <c r="H16" s="4">
         <v>9</v>
       </c>
-      <c r="I16" s="115" t="s">
+      <c r="I16" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="J16" s="115" t="s">
+      <c r="J16" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="K16" s="116" t="s">
+      <c r="K16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L16" s="122">
+      <c r="L16" s="48">
         <v>-0.01</v>
       </c>
-      <c r="M16" s="116" t="s">
+      <c r="M16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N16" s="116" t="s">
+      <c r="N16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O16" s="117" t="s">
+      <c r="O16" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="P16" s="118"/>
+      <c r="P16" s="82"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="88"/>
       <c r="D17" s="2"/>
       <c r="G17" s="10">
         <v>10</v>
       </c>
-      <c r="H17" s="114"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="116"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="118"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="82"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="2"/>
       <c r="G18" s="10">
         <v>11</v>
       </c>
-      <c r="H18" s="114"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="117"/>
-      <c r="P18" s="118"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="82"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B19" s="59"/>
-      <c r="C19" s="57"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="2"/>
       <c r="G19" s="10">
         <v>12</v>
       </c>
-      <c r="H19" s="114"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="118"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="82"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="76"/>
-      <c r="C20" s="77"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="2"/>
       <c r="G20" s="10">
         <v>13</v>
       </c>
-      <c r="H20" s="114"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="122"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="117"/>
-      <c r="P20" s="118"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="82"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B21" s="76"/>
-      <c r="C21" s="77"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="2"/>
       <c r="G21" s="10">
         <v>14</v>
       </c>
-      <c r="H21" s="114"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="122"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="117"/>
-      <c r="P21" s="118"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="82"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="76"/>
-      <c r="C22" s="77"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="2"/>
       <c r="G22" s="10">
         <v>15</v>
       </c>
-      <c r="H22" s="114"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="122"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="118"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="82"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="2"/>
       <c r="G23" s="10">
         <v>16</v>
       </c>
-      <c r="H23" s="114"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="122"/>
-      <c r="M23" s="116"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="117"/>
-      <c r="P23" s="118"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="82"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="60"/>
-      <c r="C24" s="58"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="72"/>
       <c r="D24" s="2"/>
       <c r="G24" s="10">
         <v>17</v>
       </c>
-      <c r="H24" s="114"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="116"/>
-      <c r="N24" s="116"/>
-      <c r="O24" s="117"/>
-      <c r="P24" s="118"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="82"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B25" s="59"/>
-      <c r="C25" s="57"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="2"/>
       <c r="G25" s="10">
         <v>18</v>
       </c>
-      <c r="H25" s="114"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="116"/>
-      <c r="N25" s="116"/>
-      <c r="O25" s="117"/>
-      <c r="P25" s="118"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="82"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="76"/>
-      <c r="C26" s="77"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B27" s="76"/>
-      <c r="C27" s="77"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B28" s="76"/>
-      <c r="C28" s="77"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="2"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="80"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
       <c r="N28" s="23"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B29" s="76"/>
-      <c r="C29" s="77"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="2"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="78"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
       <c r="N29" s="24"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B30" s="60"/>
-      <c r="C30" s="58"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="72"/>
       <c r="D30" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:P5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="O7:P7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -3495,22 +3493,14 @@
     <mergeCell ref="O18:P18"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:P5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="O12:P12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3538,62 +3528,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="87"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="117"/>
       <c r="M3" s="42"/>
       <c r="N3" s="42"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="C4" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55" t="s">
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="72"/>
+      <c r="L4" s="58"/>
       <c r="M4" s="43"/>
       <c r="N4" s="43"/>
     </row>
     <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="94"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="88"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="118"/>
       <c r="F5" s="13" t="s">
         <v>90</v>
       </c>
@@ -3645,6 +3635,9 @@
         <v>96</v>
       </c>
       <c r="K6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3678,6 +3671,9 @@
       <c r="K7" t="s">
         <v>121</v>
       </c>
+      <c r="L7" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
@@ -3706,6 +3702,9 @@
       <c r="K8" t="s">
         <v>121</v>
       </c>
+      <c r="L8" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
@@ -3737,6 +3736,9 @@
       <c r="K9" t="s">
         <v>121</v>
       </c>
+      <c r="L9" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
@@ -3768,6 +3770,9 @@
       <c r="K10" t="s">
         <v>121</v>
       </c>
+      <c r="L10" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
@@ -3799,6 +3804,9 @@
       <c r="K11" t="s">
         <v>121</v>
       </c>
+      <c r="L11" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
@@ -3830,6 +3838,9 @@
       <c r="K12" t="s">
         <v>97</v>
       </c>
+      <c r="L12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="13" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
@@ -3858,6 +3869,9 @@
       <c r="K13" t="s">
         <v>121</v>
       </c>
+      <c r="L13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="14" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
@@ -3891,6 +3905,9 @@
       <c r="K14" t="s">
         <v>121</v>
       </c>
+      <c r="L14" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="15" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
@@ -3922,6 +3939,9 @@
       <c r="K15" t="s">
         <v>97</v>
       </c>
+      <c r="L15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="16" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
@@ -3953,6 +3973,9 @@
       <c r="K16" t="s">
         <v>97</v>
       </c>
+      <c r="L16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
@@ -3984,6 +4007,9 @@
       <c r="K17" t="s">
         <v>97</v>
       </c>
+      <c r="L17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="12">
@@ -4015,6 +4041,9 @@
       <c r="K18" t="s">
         <v>121</v>
       </c>
+      <c r="L18" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="12">
@@ -4046,6 +4075,9 @@
       <c r="K19" t="s">
         <v>121</v>
       </c>
+      <c r="L19" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="20" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="12">
@@ -4077,6 +4109,9 @@
       <c r="K20" t="s">
         <v>97</v>
       </c>
+      <c r="L20" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="21" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="12">
@@ -4108,19 +4143,22 @@
       <c r="K21" t="s">
         <v>121</v>
       </c>
+      <c r="L21" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="22" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="123"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="14"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="123"/>
-      <c r="H22" s="123"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="123"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="14" t="s">
@@ -4134,98 +4172,98 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102"/>
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="103" t="s">
+      <c r="C25" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
       <c r="G25" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="103" t="s">
+      <c r="H25" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="106"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="103" t="s">
+      <c r="I25" s="97"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="98"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="N25" s="106"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="105"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="98"/>
+      <c r="P25" s="99"/>
     </row>
     <row r="26" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="101" t="s">
+      <c r="D26" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="101" t="s">
+      <c r="E26" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="102" t="s">
+      <c r="F26" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="111" t="s">
+      <c r="G26" s="114" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="107" t="s">
+      <c r="H26" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="I26" s="108"/>
-      <c r="J26" s="101" t="s">
+      <c r="I26" s="111"/>
+      <c r="J26" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="101" t="s">
+      <c r="K26" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="102" t="s">
+      <c r="L26" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="M26" s="112" t="s">
+      <c r="M26" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="N26" s="101" t="s">
+      <c r="N26" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="O26" s="101" t="s">
+      <c r="O26" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="102" t="s">
+      <c r="P26" s="94" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B27" s="99"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="101"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="102"/>
+      <c r="B27" s="108"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="94"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B28" s="22" t="s">
@@ -4246,10 +4284,10 @@
       <c r="G28" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="H28" s="97" t="s">
+      <c r="H28" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="98"/>
+      <c r="I28" s="107"/>
       <c r="J28" s="2">
         <v>2</v>
       </c>
@@ -4277,14 +4315,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4294,18 +4330,20 @@
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="J26:J27"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="H25:L25"/>
     <mergeCell ref="H26:I27"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="K26:K27"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J26:J27"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4315,6 +4353,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4452,22 +4505,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4483,21 +4538,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C673B99B-17E8-A44A-BCC3-BED802C36410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1C86A7-2649-C343-868A-3156ADA566F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="35840" windowHeight="22400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="146">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -164,10 +164,181 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
+    <t>Observații</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
+  </si>
+  <si>
+    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
+  </si>
+  <si>
+    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
+  </si>
+  <si>
+    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
+  </si>
+  <si>
+    <t>EC Identification</t>
+  </si>
+  <si>
+    <t>EC-based TCs</t>
+  </si>
+  <si>
+    <t>No. EC</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Valid EC</t>
+  </si>
+  <si>
+    <t>Non-valid EC</t>
+  </si>
+  <si>
+    <t>No. TCxx_EC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>input data</t>
+  </si>
+  <si>
+    <t>output data</t>
+  </si>
+  <si>
+    <t>categorie</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>BVA Condition</t>
+  </si>
+  <si>
+    <t>BVA Condition-based TCs</t>
+  </si>
+  <si>
+    <t>Crt. No.</t>
+  </si>
+  <si>
+    <t>No TCxx_BVA</t>
+  </si>
+  <si>
+    <t>BVA condition</t>
+  </si>
+  <si>
+    <t>Correlated TC</t>
+  </si>
+  <si>
+    <t>Executable</t>
+  </si>
+  <si>
+    <t>expected result</t>
+  </si>
+  <si>
+    <t>"M"</t>
+  </si>
+  <si>
+    <t>BBT TCs</t>
+  </si>
+  <si>
+    <t>Final        TC No.</t>
+  </si>
+  <si>
+    <t>Req. ID</t>
+  </si>
+  <si>
+    <t>ECP TCs</t>
+  </si>
+  <si>
+    <t>BVA TCs</t>
+  </si>
+  <si>
+    <t>actual result</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>TC1_ECP</t>
+  </si>
+  <si>
+    <t>TC3_ECP</t>
+  </si>
+  <si>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Re-testing</t>
+  </si>
+  <si>
+    <t>Regression Testing</t>
+  </si>
+  <si>
+    <t>#TCs to be run</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="17"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>passed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>failed</t>
+    </r>
+  </si>
+  <si>
+    <t>#Bugs</t>
+  </si>
+  <si>
+    <t>#Fixed Bugs</t>
+  </si>
+  <si>
+    <t>Re-tested</t>
   </si>
   <si>
     <r>
@@ -188,26 +359,270 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
+      <t xml:space="preserve"> adăugarea unui produs</t>
     </r>
   </si>
   <si>
-    <t>Observații</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
-    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
-  </si>
-  <si>
-    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
-  </si>
-  <si>
-    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
+    <t>nume is String</t>
+  </si>
+  <si>
+    <t>pret is Double</t>
+  </si>
+  <si>
+    <t>name is String</t>
+  </si>
+  <si>
+    <t>name not String</t>
+  </si>
+  <si>
+    <t>pret not Double</t>
+  </si>
+  <si>
+    <t>categorie is CategorieBautura</t>
+  </si>
+  <si>
+    <t>categorie not CategorieBautura</t>
+  </si>
+  <si>
+    <t>tip is TipBautura</t>
+  </si>
+  <si>
+    <t>tip not TipBautura</t>
+  </si>
+  <si>
+    <t>name (lungime)</t>
+  </si>
+  <si>
+    <t>nevid ("Latte")</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>pret &gt; 0</t>
+  </si>
+  <si>
+    <t>pret &lt;= 0</t>
+  </si>
+  <si>
+    <t>vid (" ")</t>
+  </si>
+  <si>
+    <t>id is int</t>
+  </si>
+  <si>
+    <t>id is Int</t>
+  </si>
+  <si>
+    <t>id not int</t>
+  </si>
+  <si>
+    <t>id &gt; 0</t>
+  </si>
+  <si>
+    <t>id &lt;= 0</t>
+  </si>
+  <si>
+    <t>1,3,5,7,9,12</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>nume</t>
+  </si>
+  <si>
+    <t>pret</t>
+  </si>
+  <si>
+    <t>tip</t>
+  </si>
+  <si>
+    <t>Latte</t>
+  </si>
+  <si>
+    <t>MILK_COFFEE</t>
+  </si>
+  <si>
+    <t>DAIRY</t>
+  </si>
+  <si>
+    <t>product added</t>
+  </si>
+  <si>
+    <t>" "</t>
+  </si>
+  <si>
+    <t>Espresso</t>
+  </si>
+  <si>
+    <t>TC4_ECP</t>
+  </si>
+  <si>
+    <t>ValidationException (nume null)</t>
+  </si>
+  <si>
+    <t>ValidationException (nume gol)</t>
+  </si>
+  <si>
+    <t>ValidationException (pret &lt;= 0)</t>
+  </si>
+  <si>
+    <t>ValidationException (categorie null)</t>
+  </si>
+  <si>
+    <t>ValidationException (tip null)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>F01.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Adăugarea unui produs nou (Product), prin atributele id, nume, pret, categorie, tip.</t>
+    </r>
+  </si>
+  <si>
+    <t>nume is string length in [1,255]</t>
+  </si>
+  <si>
+    <t>01. nume = "", length = 0</t>
+  </si>
+  <si>
+    <t>02. nume = ?, length = -1</t>
+  </si>
+  <si>
+    <t>03. nume = "M", length = 1</t>
+  </si>
+  <si>
+    <t>04. nume = "M…123", length = 255</t>
+  </si>
+  <si>
+    <t>05. nume = "M…12", length = 254</t>
+  </si>
+  <si>
+    <t>06. nume = "M…1234", length = 256</t>
+  </si>
+  <si>
+    <t>pret is float, pret&gt; 0</t>
+  </si>
+  <si>
+    <t>07. pret = 0.00</t>
+  </si>
+  <si>
+    <t>08. pret= 0.01</t>
+  </si>
+  <si>
+    <t>09. pret = -0.01</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>?(null)</t>
+  </si>
+  <si>
+    <t>ValidationException</t>
+  </si>
+  <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
+    <t>TC2_BVA</t>
+  </si>
+  <si>
+    <t>TC6_BVA</t>
+  </si>
+  <si>
+    <t>TC7_BVA</t>
+  </si>
+  <si>
+    <t>TC8_BVA</t>
+  </si>
+  <si>
+    <t>TC9_BVA</t>
+  </si>
+  <si>
+    <t>"M...12"(254)</t>
+  </si>
+  <si>
+    <t>"M...123"(255)</t>
+  </si>
+  <si>
+    <t>"M...1234"(256)</t>
+  </si>
+  <si>
+    <t>TC2_ECP</t>
+  </si>
+  <si>
+    <t>TC5_ECP</t>
+  </si>
+  <si>
+    <t>TC6_ECP</t>
+  </si>
+  <si>
+    <t>TC8_ECP</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>M...12(254)</t>
+  </si>
+  <si>
+    <t>M...123(255)</t>
+  </si>
+  <si>
+    <t>M...1234(256)</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validator doesn’t throw for max len of string being passed or null </t>
+  </si>
+  <si>
+    <t>Now validator has what it needs</t>
+  </si>
+  <si>
+    <t>1. Evidenta bauturilor dintr un shop</t>
+  </si>
+  <si>
+    <t>Un owner doreşte să îşi dezvolte un program pentru gestionarea comenzilor din magazinul sau de bauturi. Programul va permite următoarele operaţii:</t>
+  </si>
+  <si>
+    <t>F01. Adăugarea unui produs nou (Product), prin atributele id, nume, pret, categorie, tip.</t>
+  </si>
+  <si>
+    <t>addProduct(String nume, float pret, CategorieBautura categorie, TipBautura tip): void</t>
+  </si>
+  <si>
+    <t>Mitrea Ioan David</t>
+  </si>
+  <si>
+    <t>Marcu Emanuel</t>
+  </si>
+  <si>
+    <t>Mihali Gabriel</t>
   </si>
   <si>
     <r>
@@ -222,7 +637,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>title</t>
+      <t>nume</t>
     </r>
     <r>
       <rPr>
@@ -243,7 +658,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>year</t>
+      <t>pret</t>
     </r>
     <r>
       <rPr>
@@ -264,7 +679,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>title</t>
+      <t xml:space="preserve">nume </t>
     </r>
     <r>
       <rPr>
@@ -274,7 +689,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
+      <t xml:space="preserve">este un string cu lungimea validă de la 1 la 255 caractere; </t>
     </r>
     <r>
       <rPr>
@@ -285,7 +700,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>year</t>
+      <t xml:space="preserve">pret </t>
     </r>
     <r>
       <rPr>
@@ -295,433 +710,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
+      <t>este valid dacă ia valori mai mari decat 0.00.</t>
     </r>
-  </si>
-  <si>
-    <t>EC Identification</t>
-  </si>
-  <si>
-    <t>EC-based TCs</t>
-  </si>
-  <si>
-    <t>No. EC</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Valid EC</t>
-  </si>
-  <si>
-    <t>Non-valid EC</t>
-  </si>
-  <si>
-    <t>No. TCxx_EC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>input data</t>
-  </si>
-  <si>
-    <t>output data</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>BVA Condition</t>
-  </si>
-  <si>
-    <t>BVA Condition-based TCs</t>
-  </si>
-  <si>
-    <t>Crt. No.</t>
-  </si>
-  <si>
-    <t>No TCxx_BVA</t>
-  </si>
-  <si>
-    <t>BVA condition</t>
-  </si>
-  <si>
-    <t>Correlated TC</t>
-  </si>
-  <si>
-    <t>Executable</t>
-  </si>
-  <si>
-    <t>expected result</t>
-  </si>
-  <si>
-    <t>"M"</t>
-  </si>
-  <si>
-    <t>BBT TCs</t>
-  </si>
-  <si>
-    <t>Final        TC No.</t>
-  </si>
-  <si>
-    <t>Req. ID</t>
-  </si>
-  <si>
-    <t>ECP TCs</t>
-  </si>
-  <si>
-    <t>BVA TCs</t>
-  </si>
-  <si>
-    <t>actual result</t>
-  </si>
-  <si>
-    <t>F01</t>
-  </si>
-  <si>
-    <t>TC1_ECP</t>
-  </si>
-  <si>
-    <t>TC3_ECP</t>
-  </si>
-  <si>
-    <t>TC3_BVA</t>
-  </si>
-  <si>
-    <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Debugging</t>
-  </si>
-  <si>
-    <t>Re-testing</t>
-  </si>
-  <si>
-    <t>Regression Testing</t>
-  </si>
-  <si>
-    <t>#TCs to be run</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="17"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>passed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>failed</t>
-    </r>
-  </si>
-  <si>
-    <t>#Bugs</t>
-  </si>
-  <si>
-    <t>#Fixed Bugs</t>
-  </si>
-  <si>
-    <t>Re-tested</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui produs</t>
-    </r>
-  </si>
-  <si>
-    <t>nume is String</t>
-  </si>
-  <si>
-    <t>pret is Double</t>
-  </si>
-  <si>
-    <t>name is String</t>
-  </si>
-  <si>
-    <t>name not String</t>
-  </si>
-  <si>
-    <t>pret not Double</t>
-  </si>
-  <si>
-    <t>categorie is CategorieBautura</t>
-  </si>
-  <si>
-    <t>categorie not CategorieBautura</t>
-  </si>
-  <si>
-    <t>tip is TipBautura</t>
-  </si>
-  <si>
-    <t>tip not TipBautura</t>
-  </si>
-  <si>
-    <t>name (lungime)</t>
-  </si>
-  <si>
-    <t>nevid ("Latte")</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>pret &gt; 0</t>
-  </si>
-  <si>
-    <t>pret &lt;= 0</t>
-  </si>
-  <si>
-    <t>vid (" ")</t>
-  </si>
-  <si>
-    <t>id is int</t>
-  </si>
-  <si>
-    <t>id is Int</t>
-  </si>
-  <si>
-    <t>id not int</t>
-  </si>
-  <si>
-    <t>id &gt; 0</t>
-  </si>
-  <si>
-    <t>id &lt;= 0</t>
-  </si>
-  <si>
-    <t>1,3,5,7,9,12</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>nume</t>
-  </si>
-  <si>
-    <t>pret</t>
-  </si>
-  <si>
-    <t>tip</t>
-  </si>
-  <si>
-    <t>Latte</t>
-  </si>
-  <si>
-    <t>MILK_COFFEE</t>
-  </si>
-  <si>
-    <t>DAIRY</t>
-  </si>
-  <si>
-    <t>product added</t>
-  </si>
-  <si>
-    <t>" "</t>
-  </si>
-  <si>
-    <t>Espresso</t>
-  </si>
-  <si>
-    <t>TC4_ECP</t>
-  </si>
-  <si>
-    <t>ValidationException (nume null)</t>
-  </si>
-  <si>
-    <t>ValidationException (nume gol)</t>
-  </si>
-  <si>
-    <t>ValidationException (pret &lt;= 0)</t>
-  </si>
-  <si>
-    <t>ValidationException (categorie null)</t>
-  </si>
-  <si>
-    <t>ValidationException (tip null)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Adăugarea unui produs nou (Product), prin atributele id, nume, pret, categorie, tip.</t>
-    </r>
-  </si>
-  <si>
-    <t>nume is string length in [1,255]</t>
-  </si>
-  <si>
-    <t>01. nume = "", length = 0</t>
-  </si>
-  <si>
-    <t>02. nume = ?, length = -1</t>
-  </si>
-  <si>
-    <t>03. nume = "M", length = 1</t>
-  </si>
-  <si>
-    <t>04. nume = "M…123", length = 255</t>
-  </si>
-  <si>
-    <t>05. nume = "M…12", length = 254</t>
-  </si>
-  <si>
-    <t>06. nume = "M…1234", length = 256</t>
-  </si>
-  <si>
-    <t>pret is float, pret&gt; 0</t>
-  </si>
-  <si>
-    <t>07. pret = 0.00</t>
-  </si>
-  <si>
-    <t>08. pret= 0.01</t>
-  </si>
-  <si>
-    <t>09. pret = -0.01</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>?(null)</t>
-  </si>
-  <si>
-    <t>ValidationException</t>
-  </si>
-  <si>
-    <t>TC1_BVA</t>
-  </si>
-  <si>
-    <t>TC2_BVA</t>
-  </si>
-  <si>
-    <t>TC6_BVA</t>
-  </si>
-  <si>
-    <t>TC7_BVA</t>
-  </si>
-  <si>
-    <t>TC8_BVA</t>
-  </si>
-  <si>
-    <t>TC9_BVA</t>
-  </si>
-  <si>
-    <t>"M...12"(254)</t>
-  </si>
-  <si>
-    <t>"M...123"(255)</t>
-  </si>
-  <si>
-    <t>"M...1234"(256)</t>
-  </si>
-  <si>
-    <t>TC2_ECP</t>
-  </si>
-  <si>
-    <t>TC5_ECP</t>
-  </si>
-  <si>
-    <t>TC6_ECP</t>
-  </si>
-  <si>
-    <t>TC8_ECP</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>M...12(254)</t>
-  </si>
-  <si>
-    <t>M...123(255)</t>
-  </si>
-  <si>
-    <t>M...1234(256)</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validator doesn’t throw for max len of string being passed or null </t>
-  </si>
-  <si>
-    <t>Now validator has what it needs</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1702,6 +1692,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2046,6 +2037,7 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="24.5" customWidth="1"/>
     <col min="4" max="4" width="22.6640625" customWidth="1"/>
     <col min="9" max="9" width="32.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.6640625" customWidth="1"/>
@@ -2086,23 +2078,35 @@
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J4" s="2">
+        <v>234</v>
+      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J5" s="2">
+        <v>234</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="17"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="2">
+        <v>234</v>
+      </c>
     </row>
     <row r="7" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -2139,7 +2143,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2147,15 +2151,15 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>14</v>
+      <c r="B16" s="121" t="s">
+        <v>140</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2168,27 +2172,27 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B18" s="29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C20" s="27" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2205,7 +2209,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2223,7 +2227,7 @@
     <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="28"/>
       <c r="B24" s="49" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C24" s="49"/>
       <c r="D24" s="49"/>
@@ -2287,7 +2291,7 @@
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="75" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="76"/>
       <c r="D3" s="76"/>
@@ -2297,13 +2301,13 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="78" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C5" s="78"/>
       <c r="D5" s="78"/>
       <c r="E5" s="78"/>
       <c r="G5" s="64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H5" s="65"/>
       <c r="I5" s="65"/>
@@ -2316,32 +2320,32 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="I6" s="57" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>30</v>
       </c>
       <c r="J6" s="69"/>
       <c r="K6" s="69"/>
       <c r="L6" s="69"/>
       <c r="M6" s="69"/>
       <c r="N6" s="56" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O6" s="56"/>
     </row>
@@ -2350,31 +2354,31 @@
         <v>1</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E7" s="4"/>
       <c r="G7" s="80"/>
       <c r="H7" s="55"/>
       <c r="I7" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N7" s="57" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O7" s="58"/>
     </row>
@@ -2385,31 +2389,31 @@
       <c r="C8" s="70"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G8" s="40">
         <v>1</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I8" s="39">
         <v>1</v>
       </c>
       <c r="J8" s="39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K8" s="39">
         <v>15.5</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M8" s="39" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N8" s="62" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O8" s="63"/>
     </row>
@@ -2418,10 +2422,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="41">
@@ -2434,19 +2438,19 @@
         <v>2</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K9" s="39">
         <v>15.5</v>
       </c>
       <c r="L9" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M9" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="62" t="s">
         <v>96</v>
-      </c>
-      <c r="N9" s="62" t="s">
-        <v>101</v>
       </c>
       <c r="O9" s="63"/>
     </row>
@@ -2457,7 +2461,7 @@
       <c r="C10" s="70"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G10" s="41">
         <v>3</v>
@@ -2469,19 +2473,19 @@
         <v>3</v>
       </c>
       <c r="J10" s="39" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K10" s="39">
         <v>15.5</v>
       </c>
       <c r="L10" s="39" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M10" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N10" s="62" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O10" s="63"/>
     </row>
@@ -2490,10 +2494,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="71" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="41">
@@ -2506,19 +2510,19 @@
         <v>4</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K11" s="39">
         <v>-1</v>
       </c>
       <c r="L11" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M11" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N11" s="62" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O11" s="63"/>
     </row>
@@ -2529,7 +2533,7 @@
       <c r="C12" s="72"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G12" s="41">
         <v>5</v>
@@ -2541,19 +2545,19 @@
         <v>5</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K12" s="39">
         <v>15.5</v>
       </c>
       <c r="L12" s="39" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M12" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N12" s="62" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="O12" s="63"/>
     </row>
@@ -2562,10 +2566,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="41">
@@ -2578,19 +2582,19 @@
         <v>6</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K13" s="39">
         <v>15.5</v>
       </c>
       <c r="L13" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M13" s="39" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N13" s="62" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O13" s="63"/>
     </row>
@@ -2601,31 +2605,31 @@
       <c r="C14" s="74"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G14" s="40">
         <v>8</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I14" s="39">
         <v>7</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K14" s="39">
         <v>8</v>
       </c>
       <c r="L14" s="38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M14" s="38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N14" s="62" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O14" s="63"/>
     </row>
@@ -2634,10 +2638,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="70" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E15" s="4"/>
       <c r="G15" s="10"/>
@@ -2657,7 +2661,7 @@
       <c r="C16" s="70"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="8"/>
@@ -2676,7 +2680,7 @@
       <c r="C17" s="70"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="8"/>
@@ -2693,10 +2697,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="70" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E18" s="4"/>
       <c r="G18" s="9"/>
@@ -2716,7 +2720,7 @@
       <c r="C19" s="70"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="8"/>
@@ -2733,10 +2737,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="70" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E20" s="4"/>
       <c r="G20" s="10"/>
@@ -2756,7 +2760,7 @@
       <c r="C21" s="70"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
@@ -2764,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="67" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
     </row>
@@ -2777,10 +2781,10 @@
       </c>
       <c r="C23" s="68"/>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F23" s="59"/>
       <c r="G23" s="59"/>
@@ -2857,7 +2861,7 @@
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B3" s="75" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C3" s="76"/>
       <c r="D3" s="76"/>
@@ -2867,13 +2871,13 @@
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B5" s="86" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C5" s="86"/>
       <c r="D5" s="86"/>
       <c r="E5" s="3"/>
       <c r="G5" s="91" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H5" s="91"/>
       <c r="I5" s="91"/>
@@ -2887,35 +2891,35 @@
     </row>
     <row r="6" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6"/>
       <c r="G6" s="79" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I6" s="79" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J6" s="54" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K6" s="83" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L6" s="84"/>
       <c r="M6" s="84"/>
       <c r="N6" s="84"/>
       <c r="O6" s="83" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P6" s="87"/>
     </row>
@@ -2924,29 +2928,29 @@
         <v>1</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G7" s="80"/>
       <c r="H7" s="80"/>
       <c r="I7" s="80"/>
       <c r="J7" s="55"/>
       <c r="K7" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L7" s="47" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O7" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P7" s="58"/>
     </row>
@@ -2954,7 +2958,7 @@
       <c r="B8" s="88"/>
       <c r="C8" s="89"/>
       <c r="D8" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G8" s="10">
         <v>1</v>
@@ -2963,25 +2967,25 @@
         <v>1</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L8" s="48">
         <v>15.5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O8" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P8" s="82"/>
     </row>
@@ -2989,7 +2993,7 @@
       <c r="B9" s="88"/>
       <c r="C9" s="89"/>
       <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G9" s="10">
         <v>2</v>
@@ -2998,25 +3002,25 @@
         <v>2</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K9" s="45" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L9" s="48">
         <v>15.5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O9" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P9" s="82"/>
     </row>
@@ -3024,7 +3028,7 @@
       <c r="B10" s="88"/>
       <c r="C10" s="89"/>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G10" s="10">
         <v>3</v>
@@ -3033,25 +3037,25 @@
         <v>3</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L10" s="48">
         <v>15.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O10" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P10" s="82"/>
     </row>
@@ -3059,7 +3063,7 @@
       <c r="B11" s="88"/>
       <c r="C11" s="89"/>
       <c r="D11" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G11" s="10">
         <v>4</v>
@@ -3068,25 +3072,25 @@
         <v>4</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="L11" s="48">
         <v>15.5</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O11" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P11" s="82"/>
     </row>
@@ -3094,7 +3098,7 @@
       <c r="B12" s="74"/>
       <c r="C12" s="72"/>
       <c r="D12" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G12" s="10">
         <v>5</v>
@@ -3103,25 +3107,25 @@
         <v>5</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L12" s="48">
         <v>15.5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O12" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P12" s="82"/>
     </row>
@@ -3130,10 +3134,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G13" s="10">
         <v>6</v>
@@ -3142,25 +3146,25 @@
         <v>6</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K13" s="45" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L13" s="48">
         <v>15.5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O13" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P13" s="82"/>
     </row>
@@ -3168,7 +3172,7 @@
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G14" s="10">
         <v>7</v>
@@ -3177,25 +3181,25 @@
         <v>7</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L14" s="48">
         <v>0</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O14" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P14" s="82"/>
     </row>
@@ -3203,7 +3207,7 @@
       <c r="B15" s="88"/>
       <c r="C15" s="88"/>
       <c r="D15" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G15" s="10">
         <v>8</v>
@@ -3212,25 +3216,25 @@
         <v>8</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L15" s="48">
         <v>0.01</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O15" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P15" s="82"/>
     </row>
@@ -3245,25 +3249,25 @@
         <v>9</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L16" s="48">
         <v>-0.01</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O16" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P16" s="82"/>
     </row>
@@ -3516,7 +3520,7 @@
   <dimension ref="B1:P29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
     <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -3537,7 +3541,7 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="115" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
@@ -3554,26 +3558,26 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B4" s="79" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C4" s="119" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D4" s="104" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4" s="69"/>
       <c r="H4" s="69"/>
       <c r="I4" s="69"/>
       <c r="J4" s="69"/>
       <c r="K4" s="69" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L4" s="58"/>
       <c r="M4" s="43"/>
@@ -3585,25 +3589,25 @@
       <c r="D5" s="105"/>
       <c r="E5" s="118"/>
       <c r="F5" s="13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -3611,34 +3615,34 @@
         <v>1</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H6">
         <v>15.5</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
@@ -3648,31 +3652,31 @@
       </c>
       <c r="C7" s="92"/>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H7">
         <v>15.5</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
@@ -3682,10 +3686,10 @@
       </c>
       <c r="C8" s="92"/>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -3694,16 +3698,16 @@
         <v>15.5</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
@@ -3713,31 +3717,31 @@
       </c>
       <c r="C9" s="92"/>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H9">
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
@@ -3747,31 +3751,31 @@
       </c>
       <c r="C10" s="92"/>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H10">
         <v>15.5</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
@@ -3781,31 +3785,31 @@
       </c>
       <c r="C11" s="92"/>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H11">
         <v>15.5</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
@@ -3815,31 +3819,31 @@
       </c>
       <c r="C12" s="92"/>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H12">
         <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -3849,10 +3853,10 @@
       </c>
       <c r="C13" s="93"/>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -3861,16 +3865,16 @@
         <v>15.5</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3879,34 +3883,34 @@
         <v>9</v>
       </c>
       <c r="C14" s="92" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F14">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>15.5</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3916,31 +3920,31 @@
       </c>
       <c r="C15" s="92"/>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H15">
         <v>15.5</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3950,31 +3954,31 @@
       </c>
       <c r="C16" s="92"/>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F16">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H16">
         <v>15.5</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3984,31 +3988,31 @@
       </c>
       <c r="C17" s="92"/>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H17">
         <v>15.5</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4018,31 +4022,31 @@
       </c>
       <c r="C18" s="92"/>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F18">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H18">
         <v>15.5</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4052,31 +4056,31 @@
       </c>
       <c r="C19" s="92"/>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F19">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L19" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4086,31 +4090,31 @@
       </c>
       <c r="C20" s="92"/>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F20">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H20">
         <v>0.01</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4120,31 +4124,31 @@
       </c>
       <c r="C21" s="93"/>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F21">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H21">
         <v>-0.01</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -4162,7 +4166,7 @@
     </row>
     <row r="23" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
@@ -4181,23 +4185,23 @@
     </row>
     <row r="25" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C25" s="96" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D25" s="98"/>
       <c r="E25" s="98"/>
       <c r="F25" s="99"/>
       <c r="G25" s="19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H25" s="96" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I25" s="97"/>
       <c r="J25" s="98"/>
       <c r="K25" s="98"/>
       <c r="L25" s="99"/>
       <c r="M25" s="96" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N25" s="97"/>
       <c r="O25" s="98"/>
@@ -4205,47 +4209,47 @@
     </row>
     <row r="26" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="108" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C26" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="95" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="110" t="s">
         <v>62</v>
-      </c>
-      <c r="D26" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="94" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="114" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="110" t="s">
-        <v>67</v>
       </c>
       <c r="I26" s="111"/>
       <c r="J26" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="K26" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="M26" s="100" t="s">
-        <v>67</v>
-      </c>
       <c r="N26" s="95" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O26" s="95" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="P26" s="94" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
@@ -4267,7 +4271,7 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B28" s="22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C28" s="18">
         <v>10</v>
@@ -4279,13 +4283,13 @@
         <v>2</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H28" s="106" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I28" s="107"/>
       <c r="J28" s="2">
@@ -4298,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N28" s="2">
         <v>10</v>

--- a/docs/lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1C86A7-2649-C343-868A-3156ADA566F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA21A825-BE83-AA44-8A17-2156FF9A53E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1476,6 +1476,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1491,6 +1492,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1500,9 +1561,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1515,62 +1573,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1578,32 +1603,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1611,23 +1630,59 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1638,61 +1693,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2046,12 +2046,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53"/>
       <c r="H1" s="31" t="s">
         <v>1</v>
       </c>
@@ -2059,11 +2059,11 @@
       <c r="J1" s="31"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H3" s="2"/>
@@ -2158,7 +2158,7 @@
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="49" t="s">
         <v>140</v>
       </c>
       <c r="C16" s="1"/>
@@ -2226,21 +2226,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="28"/>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C26" s="30"/>
@@ -2282,41 +2282,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="G5" s="64" t="s">
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="G5" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="57"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="10" t="s">
@@ -2331,37 +2331,37 @@
       <c r="E6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="56" t="s">
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="56"/>
+      <c r="O6" s="77"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="62" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="55"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="76"/>
       <c r="I7" s="10" t="s">
         <v>85</v>
       </c>
@@ -2377,16 +2377,16 @@
       <c r="M7" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="N7" s="57" t="s">
+      <c r="N7" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="58"/>
+      <c r="O7" s="78"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="70"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>67</v>
@@ -2412,16 +2412,16 @@
       <c r="M8" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="62" t="s">
+      <c r="N8" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="O8" s="63"/>
+      <c r="O8" s="74"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="62" t="s">
         <v>65</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2449,16 +2449,16 @@
       <c r="M9" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="62" t="s">
+      <c r="N9" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="O9" s="63"/>
+      <c r="O9" s="74"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>68</v>
@@ -2484,16 +2484,16 @@
       <c r="M10" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="62" t="s">
+      <c r="N10" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="O10" s="63"/>
+      <c r="O10" s="74"/>
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="63" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="35" t="s">
@@ -2521,16 +2521,16 @@
       <c r="M11" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="62" t="s">
+      <c r="N11" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="O11" s="63"/>
+      <c r="O11" s="74"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="72"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>70</v>
@@ -2556,16 +2556,16 @@
       <c r="M12" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="62" t="s">
+      <c r="N12" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="O12" s="63"/>
+      <c r="O12" s="74"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="65" t="s">
         <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2593,16 +2593,16 @@
       <c r="M13" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="74"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="74"/>
+      <c r="C14" s="66"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>72</v>
@@ -2628,16 +2628,16 @@
       <c r="M14" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="62" t="s">
+      <c r="N14" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="O14" s="63"/>
+      <c r="O14" s="74"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="62" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -2651,14 +2651,14 @@
       <c r="K15" s="39"/>
       <c r="L15" s="39"/>
       <c r="M15" s="39"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="63"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="74"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="70"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
         <v>75</v>
@@ -2677,7 +2677,7 @@
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="70"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
         <v>78</v>
@@ -2689,14 +2689,14 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="61"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="81"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>76</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2710,14 +2710,14 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="61"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="81"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="62"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
         <v>77</v>
@@ -2729,14 +2729,14 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="61"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="81"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="62" t="s">
         <v>79</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2750,14 +2750,14 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="61"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="81"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="4">
         <v>15</v>
       </c>
-      <c r="C21" s="70"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
         <v>81</v>
@@ -2767,7 +2767,7 @@
       <c r="B22" s="36">
         <v>16</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="58" t="s">
         <v>82</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2779,18 +2779,32 @@
       <c r="B23" s="37">
         <v>17</v>
       </c>
-      <c r="C23" s="68"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
     <mergeCell ref="G5:O5"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="I6:M6"/>
@@ -2807,20 +2821,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2852,42 +2852,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="77"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="91" t="s">
+      <c r="G5" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="91"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
     </row>
     <row r="6" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
@@ -2900,43 +2900,43 @@
         <v>31</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="83" t="s">
+      <c r="K6" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="83" t="s">
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="87"/>
+      <c r="P6" s="89"/>
     </row>
     <row r="7" spans="2:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="73">
+      <c r="B7" s="65">
         <v>1</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="63" t="s">
         <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="55"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="76"/>
       <c r="K7" s="10" t="s">
         <v>86</v>
       </c>
@@ -2949,14 +2949,14 @@
       <c r="N7" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="O7" s="57" t="s">
+      <c r="O7" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="58"/>
+      <c r="P7" s="78"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="88"/>
-      <c r="C8" s="89"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="2" t="s">
         <v>104</v>
       </c>
@@ -2984,14 +2984,14 @@
       <c r="N8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="81" t="s">
+      <c r="O8" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="P8" s="82"/>
+      <c r="P8" s="91"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="83"/>
       <c r="D9" s="2" t="s">
         <v>105</v>
       </c>
@@ -3019,14 +3019,14 @@
       <c r="N9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="81" t="s">
+      <c r="O9" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="P9" s="82"/>
+      <c r="P9" s="91"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="83"/>
       <c r="D10" s="2" t="s">
         <v>106</v>
       </c>
@@ -3054,14 +3054,14 @@
       <c r="N10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O10" s="81" t="s">
+      <c r="O10" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="P10" s="82"/>
+      <c r="P10" s="91"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="2" t="s">
         <v>107</v>
       </c>
@@ -3089,14 +3089,14 @@
       <c r="N11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O11" s="81" t="s">
+      <c r="O11" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="P11" s="82"/>
+      <c r="P11" s="91"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B12" s="74"/>
-      <c r="C12" s="72"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="2" t="s">
         <v>108</v>
       </c>
@@ -3124,16 +3124,16 @@
       <c r="N12" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O12" s="81" t="s">
+      <c r="O12" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="P12" s="82"/>
+      <c r="P12" s="91"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B13" s="73">
+      <c r="B13" s="65">
         <v>2</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="65" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3163,14 +3163,14 @@
       <c r="N13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O13" s="81" t="s">
+      <c r="O13" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="P13" s="82"/>
+      <c r="P13" s="91"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="88"/>
-      <c r="C14" s="88"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
       <c r="D14" s="2" t="s">
         <v>111</v>
       </c>
@@ -3198,14 +3198,14 @@
       <c r="N14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="81" t="s">
+      <c r="O14" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="P14" s="82"/>
+      <c r="P14" s="91"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B15" s="88"/>
-      <c r="C15" s="88"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
       <c r="D15" s="2" t="s">
         <v>112</v>
       </c>
@@ -3233,14 +3233,14 @@
       <c r="N15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O15" s="81" t="s">
+      <c r="O15" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="P15" s="82"/>
+      <c r="P15" s="91"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
       <c r="D16" s="2"/>
       <c r="G16" s="10">
         <v>9</v>
@@ -3266,14 +3266,14 @@
       <c r="N16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O16" s="81" t="s">
+      <c r="O16" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="P16" s="82"/>
+      <c r="P16" s="91"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B17" s="88"/>
-      <c r="C17" s="88"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="2"/>
       <c r="G17" s="10">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       <c r="L17" s="48"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="82"/>
+      <c r="O17" s="90"/>
+      <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
       <c r="D18" s="2"/>
       <c r="G18" s="10">
         <v>11</v>
@@ -3302,12 +3302,12 @@
       <c r="L18" s="48"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="82"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="91"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B19" s="73"/>
-      <c r="C19" s="71"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="63"/>
       <c r="D19" s="2"/>
       <c r="G19" s="10">
         <v>12</v>
@@ -3319,12 +3319,12 @@
       <c r="L19" s="48"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="82"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="91"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="88"/>
-      <c r="C20" s="89"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="2"/>
       <c r="G20" s="10">
         <v>13</v>
@@ -3336,12 +3336,12 @@
       <c r="L20" s="48"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="82"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="91"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B21" s="88"/>
-      <c r="C21" s="89"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="83"/>
       <c r="D21" s="2"/>
       <c r="G21" s="10">
         <v>14</v>
@@ -3353,12 +3353,12 @@
       <c r="L21" s="48"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="82"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="91"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="88"/>
-      <c r="C22" s="89"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
       <c r="D22" s="2"/>
       <c r="G22" s="10">
         <v>15</v>
@@ -3370,12 +3370,12 @@
       <c r="L22" s="48"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="82"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="91"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="2"/>
       <c r="G23" s="10">
         <v>16</v>
@@ -3387,12 +3387,12 @@
       <c r="L23" s="48"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="82"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="91"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="74"/>
-      <c r="C24" s="72"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="2"/>
       <c r="G24" s="10">
         <v>17</v>
@@ -3404,12 +3404,12 @@
       <c r="L24" s="48"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="82"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="91"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B25" s="73"/>
-      <c r="C25" s="71"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="63"/>
       <c r="D25" s="2"/>
       <c r="G25" s="10">
         <v>18</v>
@@ -3421,50 +3421,74 @@
       <c r="L25" s="48"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="82"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="91"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B27" s="88"/>
-      <c r="C27" s="89"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B28" s="88"/>
-      <c r="C28" s="89"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="2"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
       <c r="N28" s="23"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="83"/>
       <c r="D29" s="2"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="90"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
       <c r="N29" s="24"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B30" s="74"/>
-      <c r="C30" s="72"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="64"/>
       <c r="D30" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3481,30 +3505,6 @@
     <mergeCell ref="G5:P5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="O7:P7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="O12:P12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3532,62 +3532,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="115" t="s">
+      <c r="B3" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="117"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="95"/>
       <c r="M3" s="42"/>
       <c r="N3" s="42"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="104" t="s">
+      <c r="D4" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69" t="s">
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="58"/>
+      <c r="L4" s="78"/>
       <c r="M4" s="43"/>
       <c r="N4" s="43"/>
     </row>
     <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="103"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="118"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="96"/>
       <c r="F5" s="13" t="s">
         <v>85</v>
       </c>
@@ -3614,7 +3614,7 @@
       <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="99" t="s">
         <v>46</v>
       </c>
       <c r="D6" t="s">
@@ -3650,7 +3650,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="99"/>
       <c r="D7" t="s">
         <v>126</v>
       </c>
@@ -3684,7 +3684,7 @@
         <f t="shared" ref="B8:B21" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="92"/>
+      <c r="C8" s="99"/>
       <c r="D8" t="s">
         <v>48</v>
       </c>
@@ -3715,7 +3715,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="99"/>
       <c r="D9" t="s">
         <v>95</v>
       </c>
@@ -3749,7 +3749,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="92"/>
+      <c r="C10" s="99"/>
       <c r="D10" t="s">
         <v>127</v>
       </c>
@@ -3783,7 +3783,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="92"/>
+      <c r="C11" s="99"/>
       <c r="D11" t="s">
         <v>128</v>
       </c>
@@ -3817,7 +3817,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="92"/>
+      <c r="C12" s="99"/>
       <c r="D12" t="s">
         <v>129</v>
       </c>
@@ -3851,7 +3851,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="93"/>
+      <c r="C13" s="100"/>
       <c r="D13" t="s">
         <v>29</v>
       </c>
@@ -3882,7 +3882,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="99" t="s">
         <v>46</v>
       </c>
       <c r="D14" t="s">
@@ -3918,7 +3918,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C15" s="92"/>
+      <c r="C15" s="99"/>
       <c r="D15" t="s">
         <v>29</v>
       </c>
@@ -3952,7 +3952,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C16" s="92"/>
+      <c r="C16" s="99"/>
       <c r="D16" t="s">
         <v>29</v>
       </c>
@@ -3986,7 +3986,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C17" s="92"/>
+      <c r="C17" s="99"/>
       <c r="D17" t="s">
         <v>29</v>
       </c>
@@ -4020,7 +4020,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C18" s="92"/>
+      <c r="C18" s="99"/>
       <c r="D18" t="s">
         <v>29</v>
       </c>
@@ -4054,7 +4054,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C19" s="92"/>
+      <c r="C19" s="99"/>
       <c r="D19" t="s">
         <v>29</v>
       </c>
@@ -4088,7 +4088,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C20" s="92"/>
+      <c r="C20" s="99"/>
       <c r="D20" t="s">
         <v>29</v>
       </c>
@@ -4122,7 +4122,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C21" s="93"/>
+      <c r="C21" s="100"/>
       <c r="D21" t="s">
         <v>29</v>
       </c>
@@ -4176,98 +4176,98 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="96" t="s">
+      <c r="C25" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="99"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H25" s="96" t="s">
+      <c r="H25" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="I25" s="97"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="96" t="s">
+      <c r="I25" s="113"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="N25" s="97"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="99"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="112"/>
     </row>
     <row r="26" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="108" t="s">
+      <c r="B26" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="109" t="s">
+      <c r="C26" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="95" t="s">
+      <c r="E26" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="94" t="s">
+      <c r="F26" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="114" t="s">
+      <c r="G26" s="118" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="110" t="s">
+      <c r="H26" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="111"/>
-      <c r="J26" s="95" t="s">
+      <c r="I26" s="115"/>
+      <c r="J26" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="K26" s="95" t="s">
+      <c r="K26" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="L26" s="94" t="s">
+      <c r="L26" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="M26" s="100" t="s">
+      <c r="M26" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="N26" s="95" t="s">
+      <c r="N26" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="O26" s="95" t="s">
+      <c r="O26" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="P26" s="94" t="s">
+      <c r="P26" s="109" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B27" s="108"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="101"/>
-      <c r="N27" s="95"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="94"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="108"/>
+      <c r="O27" s="108"/>
+      <c r="P27" s="109"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B28" s="22" t="s">
@@ -4288,10 +4288,10 @@
       <c r="G28" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="H28" s="106" t="s">
+      <c r="H28" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="I28" s="107"/>
+      <c r="I28" s="105"/>
       <c r="J28" s="2">
         <v>2</v>
       </c>
@@ -4319,12 +4319,13 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4341,13 +4342,12 @@
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="C14:C21"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4357,21 +4357,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4509,24 +4494,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4542,4 +4525,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>